--- a/figures_v14/figures_v14.xlsx
+++ b/figures_v14/figures_v14.xlsx
@@ -17,17 +17,17 @@
     <sheet name="FIG_5" sheetId="8" r:id="rId8"/>
     <sheet name="DATI_fig6" sheetId="9" r:id="rId9"/>
     <sheet name="FIG_6" sheetId="10" r:id="rId10"/>
-    <sheet name="DATI_fig7" sheetId="11" r:id="rId11"/>
-    <sheet name="FIG_7" sheetId="12" r:id="rId12"/>
-    <sheet name="DATI_fig8" sheetId="13" r:id="rId13"/>
-    <sheet name="FIG_8" sheetId="14" r:id="rId14"/>
+    <sheet name="DATI_fig8" sheetId="11" r:id="rId11"/>
+    <sheet name="FIG_8" sheetId="12" r:id="rId12"/>
+    <sheet name="DATI_fig9" sheetId="13" r:id="rId13"/>
+    <sheet name="FIG_9" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="94">
   <si>
     <t>Figure 2 - predicted vs true RUL, FD001. Points on the diagonal are perfect. The LLM forms horizontal bands: its output does not depend on the engine.</t>
   </si>
@@ -141,25 +141,28 @@
 6 conditions, 248 engines</t>
   </si>
   <si>
-    <t>Figure 5 - what the stated direction agrees with, per sensor. Sources: results_p0/p0_2a_report.md and results_p1/p3_5_report.md</t>
+    <t>Figure 5 - what the stated direction agrees with, per sensor. The benchmark series is computed only on the claims whose sub-dataset attests a direction for that sensor, and is blank where none does. Sources: results_p0/p0_2a_report.md and results_p1/p3_5_report.md</t>
   </si>
   <si>
     <t>Sensor</t>
   </si>
   <si>
-    <t>Agrees with the direction the prompt asserts (%)</t>
+    <t>Agrees with the reference direction (%)</t>
   </si>
   <si>
-    <t>Agrees with the direction the data shows (%)</t>
+    <t>Agrees with the empirical benchmark direction (%)</t>
   </si>
   <si>
-    <t>Agrees with the window supplied (%)</t>
+    <t>Agrees with the direction in the supplied window (%)</t>
   </si>
   <si>
     <t>Base rate, same claims (%)</t>
   </si>
   <si>
     <t>n claims</t>
+  </si>
+  <si>
+    <t>n claims where a direction is attested</t>
   </si>
   <si>
     <t>s4 (not cued)</t>
@@ -210,7 +213,7 @@
     <t>ALL</t>
   </si>
   <si>
-    <t>Figure 7 - the anchor follows the examples. Each point is one few-shot example set. Source: results_p1/p1_34_report.md</t>
+    <t>Figure 8 - the anchor follows the examples. Each point is one few-shot example set. Source: results_p1/p1_34_report.md</t>
   </si>
   <si>
     <t>Run</t>
@@ -246,7 +249,7 @@
     <t>random_seed3</t>
   </si>
   <si>
-    <t>Figure 8 - rank correlation with 95% bootstrap CI, FD001. The two reference lines are models that actually regress.</t>
+    <t>Figure 9 - rank correlation with 95% bootstrap CI, FD001. The two reference lines are models that actually regress.</t>
   </si>
   <si>
     <t>Configuration</t>
@@ -408,13 +411,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="1" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="1000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:rPr lang="en-US" sz="1000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:rPr>
               <a:t>Predicted vs true RUL, FD001 (100 engines)</a:t>
             </a:r>
@@ -3048,13 +3051,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:defRPr sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:rPr lang="en-US" sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:rPr>
                   <a:t>True RUL (cycles)</a:t>
                 </a:r>
@@ -3077,8 +3080,8 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="900" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -3112,13 +3115,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:defRPr sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:rPr lang="en-US" sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:rPr>
                   <a:t>Predicted RUL (cycles)</a:t>
                 </a:r>
@@ -3141,8 +3144,8 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="900" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -3167,8 +3170,8 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1100" baseline="0">
-              <a:latin typeface="Calibri"/>
+            <a:defRPr sz="900" baseline="0">
+              <a:latin typeface="Times New Roman"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -3204,13 +3207,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="1" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="1000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:rPr lang="en-US" sz="1000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:rPr>
               <a:t>Distribution of predicted RUL, FD001 (100 engines)</a:t>
             </a:r>
@@ -3961,13 +3964,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:defRPr sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:rPr lang="en-US" sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:rPr>
                   <a:t>Predicted RUL (cycles)</a:t>
                 </a:r>
@@ -3985,12 +3988,12 @@
           </a:ln>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr rot="-2700000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="900" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -4025,13 +4028,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:defRPr sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:rPr lang="en-US" sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:rPr>
                   <a:t>Number of engines</a:t>
                 </a:r>
@@ -4054,8 +4057,8 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="900" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -4080,8 +4083,8 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1100" baseline="0">
-              <a:latin typeface="Calibri"/>
+            <a:defRPr sz="900" baseline="0">
+              <a:latin typeface="Times New Roman"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -4117,13 +4120,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="1" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="1000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:rPr lang="en-US" sz="1000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:rPr>
               <a:t>Share of predictions on a single value, by sub-dataset (zero-shot, n = 30)</a:t>
             </a:r>
@@ -4236,11 +4239,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" baseline="0">
+                  <a:defRPr sz="900" baseline="0">
                     <a:solidFill>
                       <a:srgbClr val="1F3B57"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -4311,13 +4314,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:defRPr sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:rPr lang="en-US" sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:rPr>
                   <a:t>Sub-dataset</a:t>
                 </a:r>
@@ -4339,8 +4342,8 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="900" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -4376,13 +4379,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:defRPr sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:rPr lang="en-US" sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:rPr>
                   <a:t>Predictions on the modal value (%)</a:t>
                 </a:r>
@@ -4405,8 +4408,8 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="900" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -4452,13 +4455,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="1" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="1000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:rPr lang="en-US" sz="1000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:rPr>
               <a:t>Directional claims per sensor: what the stated direction agrees with</a:t>
             </a:r>
@@ -4481,7 +4484,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Agrees with the direction the prompt asserts (%)</c:v>
+                  <c:v>Agrees with the reference direction (%)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4565,7 +4568,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Agrees with the direction the data shows (%)</c:v>
+                  <c:v>Agrees with the empirical benchmark direction (%)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4619,7 +4622,7 @@
                   <c:v>60</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>51.11111111111111</c:v>
+                  <c:v>40</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>4.436860068259386</c:v>
@@ -4628,10 +4631,10 @@
                   <c:v>98.41605068637803</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>21.25237191650854</c:v>
+                  <c:v>34.3042071197411</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>3.420752565564424</c:v>
+                  <c:v>3.716216216216216</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>100</c:v>
@@ -4649,7 +4652,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Agrees with the window supplied (%)</c:v>
+                  <c:v>Agrees with the direction in the supplied window (%)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4825,13 +4828,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:defRPr sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:rPr lang="en-US" sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:rPr>
                   <a:t>Sensor (cued = named in the prompt)</a:t>
                 </a:r>
@@ -4853,8 +4856,8 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="900" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -4890,13 +4893,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:defRPr sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:rPr lang="en-US" sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:rPr>
                   <a:t>Percentage of directional claims</a:t>
                 </a:r>
@@ -4919,8 +4922,8 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="900" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -4945,8 +4948,8 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1100" baseline="0">
-              <a:latin typeface="Calibri"/>
+            <a:defRPr sz="900" baseline="0">
+              <a:latin typeface="Times New Roman"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -4982,13 +4985,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="1" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="1000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:rPr lang="en-US" sz="1000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:rPr>
               <a:t>Paired trend reversals and the claims that followed them (2.4%)</a:t>
             </a:r>
@@ -5032,11 +5035,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="800" baseline="0">
                     <a:solidFill>
                       <a:srgbClr val="1F3B57"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -5230,11 +5233,11 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" baseline="0">
+                  <a:defRPr sz="800" baseline="0">
                     <a:solidFill>
                       <a:srgbClr val="1F3B57"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
@@ -5313,13 +5316,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:defRPr sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:rPr lang="en-US" sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:rPr>
                   <a:t>Sensor</a:t>
                 </a:r>
@@ -5341,8 +5344,8 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="900" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -5377,13 +5380,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:defRPr sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:rPr lang="en-US" sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:rPr>
                   <a:t>Number of (engine, sensor) pairs</a:t>
                 </a:r>
@@ -5406,8 +5409,8 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="900" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -5432,8 +5435,8 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1100" baseline="0">
-              <a:latin typeface="Calibri"/>
+            <a:defRPr sz="900" baseline="0">
+              <a:latin typeface="Times New Roman"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -5469,13 +5472,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="1" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="1000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:rPr lang="en-US" sz="1000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:rPr>
               <a:t>Mean predicted RUL versus mean RUL of the few-shot examples (n = 7, r = 0.94)</a:t>
             </a:r>
@@ -5493,7 +5496,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>DATI_fig7!$C$3</c:f>
+              <c:f>DATI_fig8!$C$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5530,12 +5533,11 @@
                   <a:p>
                     <a:r>
                       <a:rPr lang="en-US"/>
-                      <a:t>asis_seed1</a:t>
+                      <a:t>asis1</a:t>
                     </a:r>
                   </a:p>
                 </c:rich>
               </c:tx>
-              <c:dLblPos val="t"/>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
@@ -5547,12 +5549,11 @@
                   <a:p>
                     <a:r>
                       <a:rPr lang="en-US"/>
-                      <a:t>strat_seed3</a:t>
+                      <a:t>strat3</a:t>
                     </a:r>
                   </a:p>
                 </c:rich>
               </c:tx>
-              <c:dLblPos val="t"/>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
@@ -5564,12 +5565,11 @@
                   <a:p>
                     <a:r>
                       <a:rPr lang="en-US"/>
-                      <a:t>strat_seed2</a:t>
+                      <a:t>strat2</a:t>
                     </a:r>
                   </a:p>
                 </c:rich>
               </c:tx>
-              <c:dLblPos val="t"/>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
@@ -5581,12 +5581,11 @@
                   <a:p>
                     <a:r>
                       <a:rPr lang="en-US"/>
-                      <a:t>strat_seed1</a:t>
+                      <a:t>strat1</a:t>
                     </a:r>
                   </a:p>
                 </c:rich>
               </c:tx>
-              <c:dLblPos val="t"/>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="4"/>
@@ -5598,12 +5597,11 @@
                   <a:p>
                     <a:r>
                       <a:rPr lang="en-US"/>
-                      <a:t>random_seed2</a:t>
+                      <a:t>rand2</a:t>
                     </a:r>
                   </a:p>
                 </c:rich>
               </c:tx>
-              <c:dLblPos val="t"/>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="5"/>
@@ -5615,12 +5613,11 @@
                   <a:p>
                     <a:r>
                       <a:rPr lang="en-US"/>
-                      <a:t>random_seed1</a:t>
+                      <a:t>rand1</a:t>
                     </a:r>
                   </a:p>
                 </c:rich>
               </c:tx>
-              <c:dLblPos val="t"/>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="6"/>
@@ -5632,29 +5629,27 @@
                   <a:p>
                     <a:r>
                       <a:rPr lang="en-US"/>
-                      <a:t>random_seed3</a:t>
+                      <a:t>rand3</a:t>
                     </a:r>
                   </a:p>
                 </c:rich>
               </c:tx>
-              <c:dLblPos val="t"/>
             </c:dLbl>
             <c:txPr>
               <a:bodyPr/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="900" baseline="0">
+                  <a:defRPr sz="800" baseline="0">
                     <a:solidFill>
                       <a:srgbClr val="8C8C8C"/>
                     </a:solidFill>
-                    <a:latin typeface="Calibri"/>
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:endParaRPr lang="en-US"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
           </c:dLbls>
           <c:trendline>
             <c:name>Linear fit</c:name>
@@ -5670,7 +5665,7 @@
           </c:trendline>
           <c:xVal>
             <c:numRef>
-              <c:f>DATI_fig7!$B$4:$B$10</c:f>
+              <c:f>DATI_fig8!$B$4:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -5700,7 +5695,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>DATI_fig7!$C$4:$C$10</c:f>
+              <c:f>DATI_fig8!$C$4:$C$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -5734,7 +5729,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>DATI_fig7!$D$3</c:f>
+              <c:f>DATI_fig8!$D$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -5756,7 +5751,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>DATI_fig7!$B$4:$B$10</c:f>
+              <c:f>DATI_fig8!$B$4:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -5786,7 +5781,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>DATI_fig7!$D$4:$D$10</c:f>
+              <c:f>DATI_fig8!$D$4:$D$10</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -5833,13 +5828,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:defRPr sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:rPr lang="en-US" sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:rPr>
                   <a:t>Mean RUL of the examples placed in the prompt</a:t>
                 </a:r>
@@ -5862,8 +5857,8 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="900" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -5897,13 +5892,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:defRPr sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:rPr lang="en-US" sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:rPr>
                   <a:t>Mean predicted RUL (100 engines)</a:t>
                 </a:r>
@@ -5926,8 +5921,8 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="900" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -5952,8 +5947,8 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1100" baseline="0">
-              <a:latin typeface="Calibri"/>
+            <a:defRPr sz="900" baseline="0">
+              <a:latin typeface="Times New Roman"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -5989,13 +5984,13 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1200" b="1" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="1000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US" sz="1200" b="1" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:rPr lang="en-US" sz="1000" b="1" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:rPr>
               <a:t>Rank correlation with the true RUL (FD001)</a:t>
             </a:r>
@@ -6028,7 +6023,7 @@
             <c:errValType val="cust"/>
             <c:plus>
               <c:numRef>
-                <c:f>'DATI_fig8'!$D$4:$D$18</c:f>
+                <c:f>'DATI_fig9'!$D$4:$D$18</c:f>
                 <c:numCache>
                   <c:formatCode>General</c:formatCode>
                   <c:ptCount val="0"/>
@@ -6037,7 +6032,7 @@
             </c:plus>
             <c:minus>
               <c:numRef>
-                <c:f>'DATI_fig8'!$C$4:$C$18</c:f>
+                <c:f>'DATI_fig9'!$C$4:$C$18</c:f>
                 <c:numCache>
                   <c:formatCode>General</c:formatCode>
                   <c:ptCount val="0"/>
@@ -6054,7 +6049,7 @@
           </c:errBars>
           <c:cat>
             <c:strRef>
-              <c:f>DATI_fig8!$A$4:$A$18</c:f>
+              <c:f>DATI_fig9!$A$4:$A$18</c:f>
               <c:strCache>
                 <c:ptCount val="15"/>
                 <c:pt idx="0">
@@ -6107,7 +6102,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>DATI_fig8!$B$4:$B$18</c:f>
+              <c:f>DATI_fig9!$B$4:$B$18</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="15"/>
@@ -6183,8 +6178,8 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="800" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -6220,13 +6215,13 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:defRPr sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US" sz="1100" baseline="0">
-                    <a:latin typeface="Calibri"/>
+                  <a:rPr lang="en-US" sz="900" baseline="0">
+                    <a:latin typeface="Times New Roman"/>
                   </a:rPr>
                   <a:t>Spearman rho</a:t>
                 </a:r>
@@ -6249,8 +6244,8 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1100" baseline="0">
-                <a:latin typeface="Calibri"/>
+              <a:defRPr sz="900" baseline="0">
+                <a:latin typeface="Times New Roman"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -6295,10 +6290,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6330,10 +6325,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6365,10 +6360,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6400,10 +6395,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6435,10 +6430,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6470,10 +6465,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6505,10 +6500,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>171450</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -8570,26 +8565,26 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -8603,7 +8598,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B5" s="3">
         <v>39.4</v>
@@ -8617,7 +8612,7 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3">
         <v>60</v>
@@ -8631,7 +8626,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B7" s="3">
         <v>62.8</v>
@@ -8645,7 +8640,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B8" s="3">
         <v>87.40000000000001</v>
@@ -8659,7 +8654,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B9" s="3">
         <v>99.2</v>
@@ -8673,7 +8668,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="3">
         <v>101.2</v>
@@ -8711,24 +8706,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>4</v>
@@ -8736,7 +8731,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B4" s="3">
         <v>-0.2107777272579729</v>
@@ -8756,7 +8751,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B5" s="3">
         <v>0.0268566269780988</v>
@@ -8776,7 +8771,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B6" s="3">
         <v>0.0276311892564081</v>
@@ -8796,7 +8791,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3">
         <v>0.0515350411981689</v>
@@ -8816,7 +8811,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B8" s="3">
         <v>0.0547709260357429</v>
@@ -8836,7 +8831,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" s="3">
         <v>0.0554564170785257</v>
@@ -8856,7 +8851,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B10" s="3">
         <v>0.0699104924278693</v>
@@ -8876,7 +8871,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B11" s="3">
         <v>0.1150591523632716</v>
@@ -8896,7 +8891,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B12" s="3">
         <v>0.1407821157098359</v>
@@ -8916,7 +8911,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B13" s="3">
         <v>0.1842360347286281</v>
@@ -8936,7 +8931,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" s="3">
         <v>0.2103369438616555</v>
@@ -8956,7 +8951,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B15" s="3">
         <v>0.2134199268903652</v>
@@ -8976,7 +8971,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B16" s="3">
         <v>0.2403850786990348</v>
@@ -8996,7 +8991,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B17" s="3">
         <v>0.2612514963110097</v>
@@ -9016,7 +9011,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B18" s="3">
         <v>0.2936431555628189</v>
@@ -9036,7 +9031,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -9516,19 +9511,19 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
-    <col min="2" max="6" width="14.7109375" customWidth="1"/>
+    <col min="2" max="7" width="14.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>37</v>
       </c>
@@ -9547,10 +9542,13 @@
       <c r="F3" s="2" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="G3" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3">
         <v>60</v>
@@ -9567,16 +9565,19 @@
       <c r="F4" s="4">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
+      <c r="G4" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="3">
         <v>51.11111111111111</v>
       </c>
       <c r="C5" s="3">
-        <v>51.11111111111111</v>
+        <v>40</v>
       </c>
       <c r="D5" s="3">
         <v>49.25925925925926</v>
@@ -9587,10 +9588,13 @@
       <c r="F5" s="4">
         <v>270</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
+      <c r="G5" s="4">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="3">
         <v>95.56313993174061</v>
@@ -9607,10 +9611,13 @@
       <c r="F6" s="4">
         <v>879</v>
       </c>
-    </row>
-    <row r="7" spans="1:6">
+      <c r="G6" s="4">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="A7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="3">
         <v>98.41605068637803</v>
@@ -9627,16 +9634,19 @@
       <c r="F7" s="4">
         <v>947</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
+      <c r="G7" s="4">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="A8" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3">
         <v>78.74762808349146</v>
       </c>
       <c r="C8" s="3">
-        <v>21.25237191650854</v>
+        <v>34.3042071197411</v>
       </c>
       <c r="D8" s="3">
         <v>47.24857685009488</v>
@@ -9647,16 +9657,19 @@
       <c r="F8" s="4">
         <v>527</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
+      <c r="G8" s="4">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B9" s="3">
         <v>96.57924743443557</v>
       </c>
       <c r="C9" s="3">
-        <v>3.420752565564424</v>
+        <v>3.716216216216216</v>
       </c>
       <c r="D9" s="3">
         <v>27.70809578107183</v>
@@ -9667,10 +9680,13 @@
       <c r="F9" s="4">
         <v>877</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
+      <c r="G9" s="4">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="A10" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B10" s="3">
         <v>100</v>
@@ -9686,6 +9702,9 @@
       </c>
       <c r="F10" s="4">
         <v>306</v>
+      </c>
+      <c r="G10" s="4">
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -9714,7 +9733,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -9722,15 +9741,15 @@
         <v>37</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4">
         <v>77</v>
@@ -9741,7 +9760,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B5" s="4">
         <v>94</v>
@@ -9752,7 +9771,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B6" s="4">
         <v>12</v>
@@ -9763,7 +9782,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" s="4">
         <v>68</v>
@@ -9774,7 +9793,7 @@
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" s="4">
         <v>2</v>
@@ -9785,7 +9804,7 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="4">
         <v>253</v>
